--- a/public/templates/matakuliah_import_template.xlsx
+++ b/public/templates/matakuliah_import_template.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="19">
   <si>
     <t>nama_matakuliah</t>
   </si>
@@ -25,25 +25,31 @@
     <t>nama_dosen</t>
   </si>
   <si>
+    <t>nama_dosen_2</t>
+  </si>
+  <si>
     <t>program_studi</t>
   </si>
   <si>
     <t>nomor_wa</t>
   </si>
   <si>
+    <t>Contoh Mata Kuliah</t>
+  </si>
+  <si>
+    <t>Nama Dosen</t>
+  </si>
+  <si>
+    <t>Informatika</t>
+  </si>
+  <si>
+    <t>081234567890</t>
+  </si>
+  <si>
     <t>tahun_ajaran</t>
   </si>
   <si>
-    <t>Contoh Mata Kuliah</t>
-  </si>
-  <si>
-    <t>Nama Dosen</t>
-  </si>
-  <si>
-    <t>Informatika</t>
-  </si>
-  <si>
-    <t>081234567890</t>
+    <t>nomor_wa_2</t>
   </si>
   <si>
     <t>Bisnis Digital</t>
@@ -423,17 +429,17 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="22.28" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="16.425" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="15.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="22.28" customWidth="true" style="0"/>
+    <col min="2" max="2" width="12.854" customWidth="true" style="0"/>
+    <col min="4" max="4" width="16.425" customWidth="true" style="0"/>
+    <col min="5" max="5" width="15.282" customWidth="true" style="0"/>
+    <col min="7" max="7" width="15.282" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -449,21 +455,29 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2"/>
+      <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
     </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>
@@ -489,27 +503,27 @@
   <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="36.42" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="36.42" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -519,12 +533,12 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -551,27 +565,27 @@
   <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="19.995" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="19.995" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
